--- a/data/Netherland_Cbw_NIS2.xlsx
+++ b/data/Netherland_Cbw_NIS2.xlsx
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="5" documentId="11_F25DC773A252ABDACC1048C8D99C6BDC5BDE58ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5730D315-6674-4C8D-BBF9-EF5D50E3E511}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-15420" yWindow="3315" windowWidth="14400" windowHeight="8175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="2010" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
